--- a/backtest_runs/20260410_193658/by_symbol/OGDC/OGDC.xlsx
+++ b/backtest_runs/20260410_193658/by_symbol/OGDC/OGDC.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
